--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominicgoj/coding/pichai/autoplasmid/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B424D7D-55FA-994D-B766-71ED520FAB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CA274B-8FB5-FE44-A8E5-1F5BF9C1B8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1880" yWindow="2160" windowWidth="26840" windowHeight="15720" xr2:uid="{10B2B5CF-2532-0648-8567-0F9B63482623}"/>
   </bookViews>
@@ -47,10 +47,10 @@
     <t>gene_seq</t>
   </si>
   <si>
-    <t>AAAAAAACCCCCCCGGGGGGGTTTTTT</t>
+    <t>AAAAAAACCCCCCCGGGGGGGTTTTTTAAAAAAACCCCCCCGGGGGGGTTTTTTAAAAAAACCCCCCCGGGGGGGTTTTTTAAAAAAACCCCCCCGGGGGGGTTTTTTAAAAAAACCCCCCCGGGGGGGTTTTTTAAAAAAACCCCCCCGGGGGGGTTTTTTAAAAAAACCCCCCCGGGGGGGTTTTTT</t>
   </si>
   <si>
-    <t>F1_MyFragment</t>
+    <t>MyFragment</t>
   </si>
 </sst>
 </file>
